--- a/rootFolder/subTest-2/Scenario-PostUser200/Main.rvl.xlsx
+++ b/rootFolder/subTest-2/Scenario-PostUser200/Main.rvl.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="RVL" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="514" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="572" uniqueCount="104">
   <si>
     <t>Flow</t>
   </si>
@@ -313,6 +314,18 @@
   </si>
   <si>
     <t>And assert name starts with field name</t>
+  </si>
+  <si>
+    <t>Tess</t>
+  </si>
+  <si>
+    <t>AssertNotNull</t>
+  </si>
+  <si>
+    <t>Then assert status code 201</t>
+  </si>
+  <si>
+    <t>apiResponse.StatusCode</t>
   </si>
 </sst>
 </file>
@@ -333,7 +346,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="224">
+  <borders count="611">
     <border>
       <left/>
       <right/>
@@ -564,11 +577,398 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="611">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -793,6 +1193,393 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="221" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="222" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="223" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="226" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="227" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="228" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="232" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="234" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="236" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="257" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="259" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="260" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="263" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="265" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="273" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="274" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="279" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="280" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="293" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="311" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="312" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="313" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="314" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="315" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="321" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="331" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="332" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="339" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="341" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="342" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="343" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="344" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="346" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="368" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="371" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="372" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="374" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="376" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="382" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="383" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="384" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="386" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="387" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="388" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="389" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="390" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="391" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="393" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="395" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="396" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="397" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="398" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="399" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="400" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="401" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="402" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="403" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="404" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="405" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="406" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="407" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="408" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="409" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="410" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="411" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="412" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="413" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="414" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="415" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="416" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="417" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="418" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="419" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="420" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="421" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="422" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="423" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="424" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="425" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="426" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="427" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="428" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="429" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="430" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="431" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="432" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="433" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="434" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="435" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="436" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="437" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="438" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="439" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="440" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="441" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="442" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="443" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="444" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="445" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="446" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="447" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="448" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="449" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="450" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="451" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="452" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="453" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="454" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="455" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="456" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="457" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="458" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="459" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="460" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="461" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="462" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="463" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="464" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="465" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="466" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="467" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="468" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="469" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="470" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="471" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="472" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="473" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="474" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="475" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="476" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="477" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="478" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="479" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="480" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="481" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="482" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="483" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="484" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="485" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="486" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="487" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="488" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="489" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="490" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="491" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="492" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="493" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="494" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="495" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="496" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="497" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="498" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="499" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="500" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="501" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="502" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="503" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="504" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="505" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="506" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="507" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="508" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="509" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="510" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="511" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="512" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="513" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="514" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="515" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="516" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="517" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="518" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="519" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="520" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="521" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="522" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="523" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="524" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="525" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="526" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="527" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="528" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="529" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="530" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="531" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="532" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="533" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="534" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="535" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="536" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="537" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="538" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="539" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="540" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="541" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="542" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="543" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="544" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="545" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="546" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="547" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="548" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="549" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="550" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="551" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="552" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="553" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="554" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="555" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="556" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="557" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="558" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="559" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="560" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="561" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="562" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="563" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="564" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="565" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="566" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="567" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="568" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="569" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="570" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="571" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="572" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="573" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="574" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="575" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="576" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="577" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="578" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="579" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="580" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="581" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="582" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="583" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="584" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="585" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="586" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="587" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="588" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="589" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="590" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="591" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="592" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="593" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="594" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="595" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="596" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="597" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="598" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="599" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="600" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="601" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="602" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="603" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="604" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="605" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="606" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="607" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="608" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="609" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="610" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.34375" customWidth="true"/>
@@ -842,654 +1629,691 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+      <c r="A2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="24"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="164" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="180"/>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="189"/>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="165" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="167" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="168"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="C9" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="24"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="164" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="180"/>
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="189"/>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="165" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="167" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="168"/>
+      <c r="D9" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="32"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="32"/>
+      <c r="A10" s="169" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="169" t="s">
+      <c r="A11" s="170"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="170"/>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="172" t="s">
-        <v>73</v>
+      <c r="A13" s="208" t="s">
+        <v>7</v>
       </c>
       <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
         <v>12</v>
       </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="208" t="s">
-        <v>7</v>
-      </c>
+      <c r="A14" s="219"/>
       <c r="B14" t="s">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="219"/>
+      <c r="A15" s="218"/>
       <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
         <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="218"/>
+      <c r="A16" s="217"/>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s">
         <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="217"/>
+      <c r="A17" s="216"/>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="215"/>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="220"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="59"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="64"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="65"/>
+      <c r="B21" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="72"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="73"/>
+      <c r="B22" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="80"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="81"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="88"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="89"/>
+      <c r="B24" s="90" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="91"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="95" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="96"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="607"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="606" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="605"/>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="604"/>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="221"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="99"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="104"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="105"/>
+      <c r="B31" s="106" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="107" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="108" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="112"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="162"/>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="163"/>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" t="s">
         <v>66</v>
       </c>
-      <c r="G17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="216"/>
-      <c r="B18" t="s">
+      <c r="G33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="222"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="185" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="187"/>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="186"/>
+      <c r="B37" t="s">
         <v>29</v>
       </c>
-      <c r="E18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="223"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="184" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="190"/>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
         <v>11</v>
       </c>
-      <c r="G18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="215"/>
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="220"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="64"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="65"/>
-      <c r="B22" s="66" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="72"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="73"/>
-      <c r="B23" s="74" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="75" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="76" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="80"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="81"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="88"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="89"/>
-      <c r="B25" s="90" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="91"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="96"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="221"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="98" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="99"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="104"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="105"/>
-      <c r="B28" s="106" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="107" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="108" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="110" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" s="112"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="162"/>
-      <c r="B29" t="s">
+      <c r="G40" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="191"/>
+      <c r="B41" t="s">
         <v>29</v>
       </c>
-      <c r="E29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E41" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" t="s">
         <v>35</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G41" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="163"/>
-      <c r="B30" t="s">
+    <row r="42">
+      <c r="A42" s="192"/>
+      <c r="B42" t="s">
         <v>29</v>
       </c>
-      <c r="E30" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E42" t="s">
+        <v>91</v>
+      </c>
+      <c r="F42" t="s">
         <v>66</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G42" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="222"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="185" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="187"/>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="186"/>
-      <c r="B34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="223"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="184" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="190"/>
-      <c r="B37" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="191"/>
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" t="s">
-        <v>90</v>
-      </c>
-      <c r="F38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="192"/>
-      <c r="B39" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" t="s">
-        <v>91</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="113"/>
-      <c r="B40" s="114" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="115"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="119"/>
-      <c r="H40" s="120"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="175" t="s">
+    <row r="43">
+      <c r="A43" s="113"/>
+      <c r="B43" s="114" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="115"/>
+      <c r="D43" s="116"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="119"/>
+      <c r="H43" s="120"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B44" t="s">
         <v>75</v>
       </c>
-      <c r="C41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="121"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="124"/>
-      <c r="E42" s="125"/>
-      <c r="F42" s="126"/>
-      <c r="G42" s="127"/>
-      <c r="H42" s="128"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="129"/>
-      <c r="B43" s="130"/>
-      <c r="C43" s="131"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="133"/>
-      <c r="F43" s="134"/>
-      <c r="G43" s="135"/>
-      <c r="H43" s="136"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="137"/>
-      <c r="B44" s="138"/>
-      <c r="C44" s="139"/>
-      <c r="D44" s="140"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="142"/>
-      <c r="G44" s="143"/>
-      <c r="H44" s="144"/>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="145"/>
-      <c r="B45" s="146"/>
-      <c r="C45" s="147"/>
-      <c r="D45" s="148"/>
-      <c r="E45" s="149"/>
-      <c r="F45" s="150"/>
-      <c r="G45" s="151"/>
-      <c r="H45" s="152"/>
+      <c r="A45" s="121"/>
+      <c r="B45" s="122"/>
+      <c r="C45" s="123"/>
+      <c r="D45" s="124"/>
+      <c r="E45" s="125"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="127"/>
+      <c r="H45" s="128"/>
     </row>
     <row r="46">
-      <c r="A46" s="153"/>
-      <c r="B46" s="154"/>
-      <c r="C46" s="155"/>
-      <c r="D46" s="156"/>
-      <c r="E46" s="157"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="159"/>
-      <c r="H46" s="160"/>
+      <c r="A46" s="129"/>
+      <c r="B46" s="130"/>
+      <c r="C46" s="131"/>
+      <c r="D46" s="132"/>
+      <c r="E46" s="133"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="135"/>
+      <c r="H46" s="136"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="137"/>
+      <c r="B47" s="138"/>
+      <c r="C47" s="139"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="141"/>
+      <c r="F47" s="142"/>
+      <c r="G47" s="143"/>
+      <c r="H47" s="144"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="145"/>
+      <c r="B48" s="146"/>
+      <c r="C48" s="147"/>
+      <c r="D48" s="148"/>
+      <c r="E48" s="149"/>
+      <c r="F48" s="150"/>
+      <c r="G48" s="151"/>
+      <c r="H48" s="152"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="153"/>
+      <c r="B49" s="154"/>
+      <c r="C49" s="155"/>
+      <c r="D49" s="156"/>
+      <c r="E49" s="157"/>
+      <c r="F49" s="158"/>
+      <c r="G49" s="159"/>
+      <c r="H49" s="160"/>
     </row>
   </sheetData>
   <tableParts/>
